--- a/anthola_fullstack/backend/exports/users-latest.xlsx
+++ b/anthola_fullstack/backend/exports/users-latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>Name</t>
   </si>
@@ -46,6 +46,24 @@
     <t>Registration date</t>
   </si>
   <si>
+    <t>ayush joshi</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>joshiayush067@gmail.com</t>
+  </si>
+  <si>
+    <t>121212</t>
+  </si>
+  <si>
+    <t>PASSENGER</t>
+  </si>
+  <si>
+    <t>2026-07-09T07:25:55.274Z</t>
+  </si>
+  <si>
     <t>anthols</t>
   </si>
   <si>
@@ -73,13 +91,7 @@
     <t>ayushi</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>ayusg@gmail.com</t>
-  </si>
-  <si>
-    <t>PASSENGER</t>
   </si>
   <si>
     <t>2026-06-18T19:09:04.906Z</t>
@@ -550,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="24" style="1" customWidth="1"/>
@@ -602,7 +614,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -617,153 +629,153 @@
         <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -777,10 +789,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>39</v>
@@ -789,33 +801,33 @@
         <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>43</v>
@@ -824,33 +836,33 @@
         <v>44</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J8" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
@@ -859,22 +871,57 @@
         <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="1">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>50</v>
+      <c r="K10" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
